--- a/api/templates/zw_device_performance/fr.xlsx
+++ b/api/templates/zw_device_performance/fr.xlsx
@@ -173,11 +173,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -547,7 +549,7 @@
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -557,35 +559,35 @@
       </c>
     </row>
     <row r="7" ht="33" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -701,25 +703,25 @@
       <c r="H6" s="1"/>
     </row>
     <row r="7" ht="17" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H7" s="1"/>

--- a/api/templates/zw_device_performance/fr.xlsx
+++ b/api/templates/zw_device_performance/fr.xlsx
@@ -29,7 +29,7 @@
     <t>LGA: &lt;Lgas&gt;</t>
   </si>
   <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+    <t>Dispositifs déclassés: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -173,13 +173,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -549,7 +547,7 @@
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -559,35 +557,35 @@
       </c>
     </row>
     <row r="7" ht="33" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -703,25 +701,25 @@
       <c r="H6" s="1"/>
     </row>
     <row r="7" ht="17" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>14</v>
       </c>
       <c r="H7" s="1"/>
